--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124354574</v>
+        <v>124353785</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490117</v>
+        <v>490242</v>
       </c>
       <c r="R2" t="n">
-        <v>6867070</v>
+        <v>6866910</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124353750</v>
+        <v>124353399</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +789,56 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490249</v>
+        <v>490485</v>
       </c>
       <c r="R3" t="n">
-        <v>6866908</v>
+        <v>6866778</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,9 +865,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +892,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -991,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124353785</v>
+        <v>124355701</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,41 +1018,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490242</v>
+        <v>490485</v>
       </c>
       <c r="R5" t="n">
-        <v>6866910</v>
+        <v>6866778</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,9 +1088,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124353399</v>
+        <v>124354574</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,56 +1139,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490485</v>
+        <v>490117</v>
       </c>
       <c r="R6" t="n">
-        <v>6866778</v>
+        <v>6867070</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,22 +1227,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124360015</v>
+        <v>124353750</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,46 +1251,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490117</v>
+        <v>490249</v>
       </c>
       <c r="R7" t="n">
-        <v>6867070</v>
+        <v>6866908</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,19 +1312,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1329,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124354006</v>
+        <v>124360015</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,31 +1353,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1382,13 +1386,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490084</v>
+        <v>490117</v>
       </c>
       <c r="R8" t="n">
-        <v>6866988</v>
+        <v>6867070</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,9 +1419,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,22 +1446,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124355701</v>
+        <v>124354006</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,50 +1470,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490485</v>
+        <v>490084</v>
       </c>
       <c r="R9" t="n">
-        <v>6866778</v>
+        <v>6866988</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,19 +1536,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,12 +1553,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124353399</v>
+        <v>124355701</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -867,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124353772</v>
+        <v>124354006</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +914,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490241</v>
+        <v>490084</v>
       </c>
       <c r="R4" t="n">
-        <v>6866912</v>
+        <v>6866988</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124355701</v>
+        <v>124360015</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,50 +1017,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490485</v>
+        <v>490117</v>
       </c>
       <c r="R5" t="n">
-        <v>6866778</v>
+        <v>6867070</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1110,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124354574</v>
+        <v>124353399</v>
       </c>
       <c r="B6" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,41 +1134,56 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490117</v>
+        <v>490485</v>
       </c>
       <c r="R6" t="n">
-        <v>6867070</v>
+        <v>6866778</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124353750</v>
+        <v>124353772</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,21 +1265,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490249</v>
+        <v>490241</v>
       </c>
       <c r="R7" t="n">
-        <v>6866908</v>
+        <v>6866912</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124360015</v>
+        <v>124354574</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,33 +1363,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
@@ -1392,7 +1397,7 @@
         <v>6867070</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,7 +1463,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124354006</v>
+        <v>124353750</v>
       </c>
       <c r="B9" t="n">
         <v>57666</v>
@@ -1492,21 +1497,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490084</v>
+        <v>490249</v>
       </c>
       <c r="R9" t="n">
-        <v>6866988</v>
+        <v>6866908</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124353785</v>
+        <v>124360015</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490242</v>
+        <v>490117</v>
       </c>
       <c r="R2" t="n">
-        <v>6866910</v>
+        <v>6867070</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +753,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124355701</v>
+        <v>124353785</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,50 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490485</v>
+        <v>490242</v>
       </c>
       <c r="R3" t="n">
-        <v>6866778</v>
+        <v>6866910</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,19 +865,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124354006</v>
+        <v>124354574</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,42 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490084</v>
+        <v>490117</v>
       </c>
       <c r="R4" t="n">
-        <v>6866988</v>
+        <v>6867070</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,9 +967,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,19 +994,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124360015</v>
+        <v>124353399</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1039,24 +1040,34 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490117</v>
+        <v>490485</v>
       </c>
       <c r="R5" t="n">
-        <v>6867070</v>
+        <v>6866778</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124353399</v>
+        <v>124353772</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,56 +1145,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490485</v>
+        <v>490241</v>
       </c>
       <c r="R6" t="n">
-        <v>6866778</v>
+        <v>6866912</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,19 +1206,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1223,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124353772</v>
+        <v>124354006</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,34 +1251,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490241</v>
+        <v>490084</v>
       </c>
       <c r="R7" t="n">
-        <v>6866912</v>
+        <v>6866988</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124354574</v>
+        <v>124355701</v>
       </c>
       <c r="B8" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,41 +1354,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490117</v>
+        <v>490485</v>
       </c>
       <c r="R8" t="n">
-        <v>6867070</v>
+        <v>6866778</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,12 +1451,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124360015</v>
+        <v>124354006</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490117</v>
+        <v>490084</v>
       </c>
       <c r="R2" t="n">
-        <v>6867070</v>
+        <v>6866988</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,19 +753,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124353785</v>
+        <v>124355701</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +794,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490242</v>
+        <v>490485</v>
       </c>
       <c r="R3" t="n">
-        <v>6866910</v>
+        <v>6866778</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,9 +864,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124354574</v>
+        <v>124360015</v>
       </c>
       <c r="B4" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,28 +915,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
@@ -940,7 +954,7 @@
         <v>6867070</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124353399</v>
+        <v>124353785</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,56 +1032,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490485</v>
+        <v>490242</v>
       </c>
       <c r="R5" t="n">
-        <v>6866778</v>
+        <v>6866910</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,19 +1093,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1110,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124353772</v>
+        <v>124353399</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,41 +1134,56 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490241</v>
+        <v>490485</v>
       </c>
       <c r="R6" t="n">
-        <v>6866912</v>
+        <v>6866778</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,9 +1210,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124354006</v>
+        <v>124353772</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,39 +1265,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490084</v>
+        <v>490241</v>
       </c>
       <c r="R7" t="n">
-        <v>6866988</v>
+        <v>6866912</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124355701</v>
+        <v>124353750</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,50 +1363,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490485</v>
+        <v>490249</v>
       </c>
       <c r="R8" t="n">
-        <v>6866778</v>
+        <v>6866908</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,19 +1424,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,22 +1441,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124353750</v>
+        <v>124354574</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1469,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,13 +1493,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490249</v>
+        <v>490117</v>
       </c>
       <c r="R9" t="n">
-        <v>6866908</v>
+        <v>6867070</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,9 +1526,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,12 +1553,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124355701</v>
+        <v>124353750</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,50 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490485</v>
+        <v>490249</v>
       </c>
       <c r="R3" t="n">
-        <v>6866778</v>
+        <v>6866908</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,19 +855,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124360015</v>
+        <v>124354574</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,33 +896,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
@@ -954,7 +930,7 @@
         <v>6867070</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124353785</v>
+        <v>124355701</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,41 +1008,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490242</v>
+        <v>490485</v>
       </c>
       <c r="R5" t="n">
-        <v>6866910</v>
+        <v>6866778</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,9 +1078,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124353399</v>
+        <v>124353785</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,56 +1129,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490485</v>
+        <v>490242</v>
       </c>
       <c r="R6" t="n">
-        <v>6866778</v>
+        <v>6866910</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,19 +1190,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1207,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124353772</v>
+        <v>124360015</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,41 +1231,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490241</v>
+        <v>490117</v>
       </c>
       <c r="R7" t="n">
-        <v>6866912</v>
+        <v>6867070</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,9 +1297,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,22 +1324,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124353750</v>
+        <v>124353772</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490249</v>
+        <v>490241</v>
       </c>
       <c r="R8" t="n">
-        <v>6866908</v>
+        <v>6866912</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124354574</v>
+        <v>124353399</v>
       </c>
       <c r="B9" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,41 +1450,56 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490117</v>
+        <v>490485</v>
       </c>
       <c r="R9" t="n">
-        <v>6867070</v>
+        <v>6866778</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,12 +1553,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124354006</v>
+        <v>124355701</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490084</v>
+        <v>490485</v>
       </c>
       <c r="R2" t="n">
-        <v>6866988</v>
+        <v>6866778</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,9 +757,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124353750</v>
+        <v>124354574</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490249</v>
+        <v>490117</v>
       </c>
       <c r="R3" t="n">
-        <v>6866908</v>
+        <v>6867070</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,9 +869,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124354574</v>
+        <v>124353785</v>
       </c>
       <c r="B4" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490117</v>
+        <v>490242</v>
       </c>
       <c r="R4" t="n">
-        <v>6867070</v>
+        <v>6866910</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,19 +981,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +998,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124355701</v>
+        <v>124354006</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,50 +1022,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490485</v>
+        <v>490084</v>
       </c>
       <c r="R5" t="n">
-        <v>6866778</v>
+        <v>6866988</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,19 +1088,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124353785</v>
+        <v>124353772</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490242</v>
+        <v>490241</v>
       </c>
       <c r="R6" t="n">
-        <v>6866910</v>
+        <v>6866912</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124360015</v>
+        <v>124353750</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,46 +1231,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490117</v>
+        <v>490249</v>
       </c>
       <c r="R7" t="n">
-        <v>6867070</v>
+        <v>6866908</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,19 +1292,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,22 +1309,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124353772</v>
+        <v>124353399</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,41 +1333,56 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490241</v>
+        <v>490485</v>
       </c>
       <c r="R8" t="n">
-        <v>6866912</v>
+        <v>6866778</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,9 +1409,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,19 +1436,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124353399</v>
+        <v>124360015</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1472,34 +1482,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490485</v>
+        <v>490117</v>
       </c>
       <c r="R9" t="n">
-        <v>6866778</v>
+        <v>6867070</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,12 +1553,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1795,6 +1795,122 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124353929</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92305</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Korpåsen, Korpåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>490215</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6866944</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124355701</v>
+        <v>124354006</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490485</v>
+        <v>490084</v>
       </c>
       <c r="R2" t="n">
-        <v>6866778</v>
+        <v>6866988</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,19 +753,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124354574</v>
+        <v>124360015</v>
       </c>
       <c r="B3" t="n">
-        <v>79428</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,28 +794,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
@@ -842,7 +833,7 @@
         <v>6867070</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124353785</v>
+        <v>124354574</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490242</v>
+        <v>490117</v>
       </c>
       <c r="R4" t="n">
-        <v>6866910</v>
+        <v>6867070</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,9 +972,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124354006</v>
+        <v>124355701</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,46 +1023,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490084</v>
+        <v>490485</v>
       </c>
       <c r="R5" t="n">
-        <v>6866988</v>
+        <v>6866778</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,9 +1093,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,12 +1120,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1219,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124353750</v>
+        <v>124353399</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,41 +1246,56 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490249</v>
+        <v>490485</v>
       </c>
       <c r="R7" t="n">
-        <v>6866908</v>
+        <v>6866778</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,9 +1322,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,22 +1349,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124353399</v>
+        <v>124353785</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,56 +1373,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490485</v>
+        <v>490242</v>
       </c>
       <c r="R8" t="n">
-        <v>6866778</v>
+        <v>6866910</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,19 +1434,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,22 +1451,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124360015</v>
+        <v>124353750</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,46 +1475,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490117</v>
+        <v>490249</v>
       </c>
       <c r="R9" t="n">
-        <v>6867070</v>
+        <v>6866908</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,19 +1536,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,12 +1553,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124355701</v>
+        <v>124353772</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,50 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490485</v>
+        <v>490241</v>
       </c>
       <c r="R5" t="n">
-        <v>6866778</v>
+        <v>6866912</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,19 +1084,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124353772</v>
+        <v>124355701</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,41 +1125,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490241</v>
+        <v>490485</v>
       </c>
       <c r="R6" t="n">
-        <v>6866912</v>
+        <v>6866778</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,9 +1195,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,12 +1222,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124354006</v>
+        <v>124353785</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490084</v>
+        <v>490242</v>
       </c>
       <c r="R2" t="n">
-        <v>6866988</v>
+        <v>6866910</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124354574</v>
+        <v>124355701</v>
       </c>
       <c r="B4" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,41 +906,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490117</v>
+        <v>490485</v>
       </c>
       <c r="R4" t="n">
-        <v>6867070</v>
+        <v>6866778</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,12 +1003,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1113,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124355701</v>
+        <v>124353399</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,35 +1129,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1197,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124353399</v>
+        <v>124354574</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,56 +1256,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490485</v>
+        <v>490117</v>
       </c>
       <c r="R7" t="n">
-        <v>6866778</v>
+        <v>6867070</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1344,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124353785</v>
+        <v>124353750</v>
       </c>
       <c r="B8" t="n">
-        <v>78546</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490242</v>
+        <v>490249</v>
       </c>
       <c r="R8" t="n">
-        <v>6866910</v>
+        <v>6866908</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1463,7 +1458,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124353750</v>
+        <v>124354006</v>
       </c>
       <c r="B9" t="n">
         <v>57666</v>
@@ -1497,16 +1492,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490249</v>
+        <v>490084</v>
       </c>
       <c r="R9" t="n">
-        <v>6866908</v>
+        <v>6866988</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124353785</v>
+        <v>124354574</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490242</v>
+        <v>490117</v>
       </c>
       <c r="R2" t="n">
-        <v>6866910</v>
+        <v>6867070</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +748,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -894,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124355701</v>
+        <v>124354006</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,50 +916,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490485</v>
+        <v>490084</v>
       </c>
       <c r="R4" t="n">
-        <v>6866778</v>
+        <v>6866988</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,19 +982,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124353772</v>
+        <v>124353750</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490241</v>
+        <v>490249</v>
       </c>
       <c r="R5" t="n">
-        <v>6866912</v>
+        <v>6866908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124353399</v>
+        <v>124355701</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,41 +1125,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1207,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124354574</v>
+        <v>124353785</v>
       </c>
       <c r="B7" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1250,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490117</v>
+        <v>490242</v>
       </c>
       <c r="R7" t="n">
-        <v>6867070</v>
+        <v>6866910</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,19 +1307,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,22 +1324,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124353750</v>
+        <v>124353399</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,41 +1348,56 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490249</v>
+        <v>490485</v>
       </c>
       <c r="R8" t="n">
-        <v>6866908</v>
+        <v>6866778</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1429,9 +1424,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,22 +1451,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124354006</v>
+        <v>124353772</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,39 +1479,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490084</v>
+        <v>490241</v>
       </c>
       <c r="R9" t="n">
-        <v>6866988</v>
+        <v>6866912</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124360015</v>
+        <v>124353785</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,46 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490117</v>
+        <v>490242</v>
       </c>
       <c r="R3" t="n">
-        <v>6867070</v>
+        <v>6866910</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,19 +860,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124354006</v>
+        <v>124353399</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,46 +901,56 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490084</v>
+        <v>490485</v>
       </c>
       <c r="R4" t="n">
-        <v>6866988</v>
+        <v>6866778</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,9 +977,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124353750</v>
+        <v>124360015</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,41 +1028,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490249</v>
+        <v>490117</v>
       </c>
       <c r="R5" t="n">
-        <v>6866908</v>
+        <v>6867070</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,9 +1094,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124355701</v>
+        <v>124354006</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,50 +1145,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490485</v>
+        <v>490084</v>
       </c>
       <c r="R6" t="n">
-        <v>6866778</v>
+        <v>6866988</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,19 +1211,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124353785</v>
+        <v>124355701</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,41 +1252,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490242</v>
+        <v>490485</v>
       </c>
       <c r="R7" t="n">
-        <v>6866910</v>
+        <v>6866778</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,9 +1322,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,22 +1349,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124353399</v>
+        <v>124353772</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,56 +1373,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490485</v>
+        <v>490241</v>
       </c>
       <c r="R8" t="n">
-        <v>6866778</v>
+        <v>6866912</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,19 +1434,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,22 +1451,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124353772</v>
+        <v>124353750</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1479,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490241</v>
+        <v>490249</v>
       </c>
       <c r="R9" t="n">
-        <v>6866912</v>
+        <v>6866908</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124354574</v>
+        <v>124354006</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490117</v>
+        <v>490084</v>
       </c>
       <c r="R2" t="n">
-        <v>6867070</v>
+        <v>6866988</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +753,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124353785</v>
+        <v>124354574</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490242</v>
+        <v>490117</v>
       </c>
       <c r="R3" t="n">
-        <v>6866910</v>
+        <v>6867070</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,9 +855,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124353399</v>
+        <v>124353772</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,56 +906,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490485</v>
+        <v>490241</v>
       </c>
       <c r="R4" t="n">
-        <v>6866778</v>
+        <v>6866912</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,19 +967,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124360015</v>
+        <v>124353750</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,46 +1008,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490117</v>
+        <v>490249</v>
       </c>
       <c r="R5" t="n">
-        <v>6867070</v>
+        <v>6866908</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,19 +1069,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124354006</v>
+        <v>124353785</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>78546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490084</v>
+        <v>490242</v>
       </c>
       <c r="R6" t="n">
-        <v>6866988</v>
+        <v>6866910</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1361,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124353772</v>
+        <v>124360015</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,41 +1333,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490241</v>
+        <v>490117</v>
       </c>
       <c r="R8" t="n">
-        <v>6866912</v>
+        <v>6867070</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,9 +1399,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,22 +1426,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124353750</v>
+        <v>124353399</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,41 +1450,56 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490249</v>
+        <v>490485</v>
       </c>
       <c r="R9" t="n">
-        <v>6866908</v>
+        <v>6866778</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,9 +1526,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,12 +1553,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124354574</v>
+        <v>124353772</v>
       </c>
       <c r="B3" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490117</v>
+        <v>490241</v>
       </c>
       <c r="R3" t="n">
-        <v>6867070</v>
+        <v>6866912</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,19 +855,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124353772</v>
+        <v>124354574</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490241</v>
+        <v>490117</v>
       </c>
       <c r="R4" t="n">
-        <v>6866912</v>
+        <v>6867070</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,9 +957,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124354006</v>
+        <v>124353399</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,56 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490084</v>
+        <v>490485</v>
       </c>
       <c r="R2" t="n">
-        <v>6866988</v>
+        <v>6866778</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,9 +763,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +790,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124353772</v>
+        <v>124353785</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +818,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490241</v>
+        <v>490242</v>
       </c>
       <c r="R3" t="n">
-        <v>6866912</v>
+        <v>6866910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124354574</v>
+        <v>124355701</v>
       </c>
       <c r="B4" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +916,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490117</v>
+        <v>490485</v>
       </c>
       <c r="R4" t="n">
-        <v>6867070</v>
+        <v>6866778</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +1013,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124353750</v>
+        <v>124354006</v>
       </c>
       <c r="B5" t="n">
         <v>57666</v>
@@ -1030,16 +1059,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490249</v>
+        <v>490084</v>
       </c>
       <c r="R5" t="n">
-        <v>6866908</v>
+        <v>6866988</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124353785</v>
+        <v>124360015</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,41 +1144,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490242</v>
+        <v>490117</v>
       </c>
       <c r="R6" t="n">
-        <v>6866910</v>
+        <v>6867070</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,9 +1210,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124355701</v>
+        <v>124353750</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,50 +1261,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490485</v>
+        <v>490249</v>
       </c>
       <c r="R7" t="n">
-        <v>6866778</v>
+        <v>6866908</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,19 +1322,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,22 +1339,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124360015</v>
+        <v>124354574</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,33 +1363,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
@@ -1372,7 +1397,7 @@
         <v>6867070</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1401,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1411,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124353399</v>
+        <v>124353772</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,56 +1475,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490485</v>
+        <v>490241</v>
       </c>
       <c r="R9" t="n">
-        <v>6866778</v>
+        <v>6866912</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,19 +1536,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,12 +1553,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124353399</v>
+        <v>124353772</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,56 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490485</v>
+        <v>490241</v>
       </c>
       <c r="R2" t="n">
-        <v>6866778</v>
+        <v>6866912</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,19 +748,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -904,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124355701</v>
+        <v>124354006</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,50 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490485</v>
+        <v>490084</v>
       </c>
       <c r="R4" t="n">
-        <v>6866778</v>
+        <v>6866988</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,19 +957,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124354006</v>
+        <v>124353399</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,46 +998,56 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490084</v>
+        <v>490485</v>
       </c>
       <c r="R5" t="n">
-        <v>6866988</v>
+        <v>6866778</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,9 +1074,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124360015</v>
+        <v>124353750</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,46 +1125,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490117</v>
+        <v>490249</v>
       </c>
       <c r="R6" t="n">
-        <v>6867070</v>
+        <v>6866908</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,19 +1186,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124353750</v>
+        <v>124360015</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,41 +1227,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490249</v>
+        <v>490117</v>
       </c>
       <c r="R7" t="n">
-        <v>6866908</v>
+        <v>6867070</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,9 +1293,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,22 +1320,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124354574</v>
+        <v>124355701</v>
       </c>
       <c r="B8" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,41 +1344,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490117</v>
+        <v>490485</v>
       </c>
       <c r="R8" t="n">
-        <v>6867070</v>
+        <v>6866778</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,22 +1441,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124353772</v>
+        <v>124354574</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,21 +1469,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,13 +1493,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490241</v>
+        <v>490117</v>
       </c>
       <c r="R9" t="n">
-        <v>6866912</v>
+        <v>6867070</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,9 +1526,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,12 +1553,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -1688,7 +1688,7 @@
         <v>124353831</v>
       </c>
       <c r="B11" t="n">
-        <v>78905</v>
+        <v>79042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>124353929</v>
       </c>
       <c r="B12" t="n">
-        <v>92305</v>
+        <v>92460</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -1802,11 +1802,6 @@
       <c r="B12" t="n">
         <v>92460</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>LC</t>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124353772</v>
+        <v>124353831</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490241</v>
+        <v>490485</v>
       </c>
       <c r="R2" t="n">
-        <v>6866912</v>
+        <v>6866778</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +743,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124353785</v>
+        <v>124353929</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490242</v>
+        <v>490215</v>
       </c>
       <c r="R3" t="n">
-        <v>6866910</v>
+        <v>6866944</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,44 +853,50 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124354006</v>
+        <v>124353785</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,39 +904,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490084</v>
+        <v>490242</v>
       </c>
       <c r="R4" t="n">
-        <v>6866988</v>
+        <v>6866910</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,68 +990,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124353399</v>
+        <v>124354574</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490485</v>
+        <v>490117</v>
       </c>
       <c r="R5" t="n">
-        <v>6866778</v>
+        <v>6867070</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,7 +1060,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1086,7 +1070,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,65 +1085,75 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124353750</v>
+        <v>124353399</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Korpåsen, Korpåsen, Hls</t>
+          <t>Pultjärnen, Pultjärnen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490249</v>
+        <v>490485</v>
       </c>
       <c r="R6" t="n">
-        <v>6866908</v>
+        <v>6866778</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,9 +1180,19 @@
           <t>2025-04-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,12 +1207,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1218,12 +1222,7 @@
         <v>124360015</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,62 +1331,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124355701</v>
+        <v>124359986</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pultjärnen, Pultjärnen, Hls</t>
+          <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490485</v>
+        <v>490117</v>
       </c>
       <c r="R8" t="n">
-        <v>6866778</v>
+        <v>6867070</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,27 +1434,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124354574</v>
+        <v>124353750</v>
       </c>
       <c r="B9" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,21 +1457,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,13 +1481,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490117</v>
+        <v>490249</v>
       </c>
       <c r="R9" t="n">
-        <v>6867070</v>
+        <v>6866908</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,19 +1514,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,73 +1531,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124359986</v>
+        <v>124354006</v>
       </c>
       <c r="B10" t="n">
-        <v>56725</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102613</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490117</v>
+        <v>490084</v>
       </c>
       <c r="R10" t="n">
-        <v>6867070</v>
+        <v>6866988</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,19 +1616,9 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,52 +1633,56 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124353831</v>
+        <v>124355701</v>
       </c>
       <c r="B11" t="n">
-        <v>79042</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>967</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pultjärnen, Pultjärnen, Hls</t>
@@ -1760,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1770,7 +1734,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,51 +1761,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124353929</v>
+        <v>124353772</v>
       </c>
       <c r="B12" t="n">
-        <v>92460</v>
+        <v>79085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Korpåsen, Korpåsen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490215</v>
+        <v>490241</v>
       </c>
       <c r="R12" t="n">
-        <v>6866944</v>
+        <v>6866912</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1868,40 +1829,29 @@
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-23</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 53354-2024 artfynd.xlsx
+++ b/artfynd/A 53354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124353831</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124353929</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124353785</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124354574</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124353399</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124360015</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1443,6 +1478,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124359986</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124353750</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124354006</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124355701</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1855,8 +1910,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124353772</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>